--- a/output/pdf_financials_xlsx/MSR.xlsx
+++ b/output/pdf_financials_xlsx/MSR.xlsx
@@ -5807,52 +5807,52 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.550011</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.658676</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-1.441063</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-2.500779</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-3.293847</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-5.179484</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-6.624296</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>-8.233676000000001</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-3.424646</v>
+        <v>-3.843569</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-4.714327</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-5.094522</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-2.995052</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-0.524973</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-1.26222</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>5.776042</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-0.196807</v>
       </c>
     </row>
     <row r="92">
@@ -5898,19 +5898,19 @@
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.648471</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.121122</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>11.232606</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>13.077248</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>13.507185</v>
       </c>
     </row>
     <row r="93">
@@ -9170,7 +9170,11 @@
           <t>Share-based payment reserve (note 9)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -9267,7 +9271,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -11071,7 +11079,11 @@
           <t>Share-based payment reserve (note 8)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11558,7 +11570,11 @@
           <t>Share-based payment reserve (note 8 and 9)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -17296,7 +17312,11 @@
           <t>Cumulative Translation Reserve</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MSR.xlsx
+++ b/output/pdf_financials_xlsx/MSR.xlsx
@@ -1032,52 +1032,52 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010236</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011302</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006254</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001527</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00042</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001794</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001592</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001348</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000781</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000434</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004154</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00825</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000768</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000421</v>
       </c>
     </row>
     <row r="13">
@@ -1992,52 +1992,52 @@
         <v>-0.070851</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.041359</v>
+        <v>-0.031123</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.047227</v>
+        <v>-0.035925</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.684406</v>
+        <v>-0.678152</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.216715</v>
+        <v>-0.215188</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.385722</v>
+        <v>-0.385302</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.261937</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.685334</v>
+        <v>-0.68354</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.545932</v>
+        <v>-0.54434</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.397622</v>
+        <v>-0.396274</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.074476</v>
+        <v>-1.073695</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.233546</v>
+        <v>-3.233112</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-3.603483</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.220279</v>
+        <v>-7.216125</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-19.780292</v>
+        <v>-19.772042</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>16.158772</v>
+        <v>16.15954</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.989252</v>
+        <v>-1.988831</v>
       </c>
     </row>
     <row r="28">
@@ -2108,52 +2108,52 @@
         <v>-0.070851</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.041359</v>
+        <v>-0.031123</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.047227</v>
+        <v>-0.035925</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.684406</v>
+        <v>-0.678152</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.216715</v>
+        <v>-0.215188</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.385722</v>
+        <v>-0.385302</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.261937</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.685334</v>
+        <v>-0.68354</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.545932</v>
+        <v>-0.54434</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.397622</v>
+        <v>-0.396274</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.074476</v>
+        <v>-1.073695</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.233546</v>
+        <v>-3.233112</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-3.603483</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.220279</v>
+        <v>-7.216125</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-19.780292</v>
+        <v>-19.772042</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>16.158772</v>
+        <v>16.15954</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.989252</v>
+        <v>-1.988831</v>
       </c>
     </row>
     <row r="30">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.371758</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.13478</v>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.371758</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.13478</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.371758</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.045545</v>
@@ -18120,7 +18120,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -38924,7 +38924,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">

--- a/output/pdf_financials_xlsx/MSR.xlsx
+++ b/output/pdf_financials_xlsx/MSR.xlsx
@@ -763,10 +763,10 @@
         <v>0.304271</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.304692</v>
+        <v>0.307692</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.292889</v>
+        <v>0.357089</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0.335001</v>
@@ -937,10 +937,10 @@
         <v>0.304271</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.304692</v>
+        <v>0.307692</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.292889</v>
+        <v>0.357089</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0.335001</v>
@@ -995,10 +995,10 @@
         <v>-0.304271</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.304692</v>
+        <v>-0.307692</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.292889</v>
+        <v>-0.357089</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-0.335001</v>
@@ -7165,13 +7165,13 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.181664</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.237484</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -26154,7 +26154,11 @@
           <t>Net proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -36404,7 +36408,11 @@
           <t>Directors' fees (note 12(i)(f))</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -36451,7 +36459,7 @@
         </is>
       </c>
       <c r="N289" s="5" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -37762,7 +37770,11 @@
           <t>Directors' fees (note 11(f))</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -37807,7 +37819,7 @@
         <v>0.003</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
